--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0025.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0025.xlsx
@@ -6554,7 +6554,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Yes.</t>
+          <t>Đúng vậy.</t>
         </is>
       </c>
     </row>
@@ -7074,7 +7074,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Yes.</t>
+          <t>Đúng vậy.</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Nhưng dù sao, ta vẫn lừa hắn...</t>
+          <t>Nhưng dù sao, tao vẫn lừa hắn...</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>À, cậu chính là Rover phải không?</t>
+          <t>À, cậu chính là Vận Mệnh Giả phải không?</t>
         </is>
       </c>
     </row>
@@ -9999,7 +9999,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Giống như KU-Money và KU-Tolo, ta phụ trách khu vực này.</t>
+          <t>Giống như KU-Money và KU-Tolo, tao phụ trách khu vực này.</t>
         </is>
       </c>
     </row>
@@ -11689,7 +11689,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Cậu định nuốt chửng mớ hỗn độn gì đấy?! Đói thì kiếm cái gì tử tế mà ăn đi. Cái này? Tuyệt đối không!</t>
+          <t>Mày định nuốt chửng mớ hỗn độn gì đấy?! Đói thì kiếm cái gì tử tế mà ăn đi. Cái này? Tuyệt đối không!</t>
         </is>
       </c>
     </row>
@@ -12144,7 +12144,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Không, ta đang nói về con quái vật kia...</t>
+          <t>Không, tao đang nói về con quái vật kia...</t>
         </is>
       </c>
     </row>
@@ -12274,7 +12274,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Ta thấy ổn mà.</t>
+          <t>Tao thấy ổn mà.</t>
         </is>
       </c>
     </row>
@@ -12794,7 +12794,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Hello?</t>
+          <t>Xin chào?</t>
         </is>
       </c>
     </row>
@@ -14614,7 +14614,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Anh biết tôi à?</t>
+          <t>Cậu biết tớ à?</t>
         </is>
       </c>
     </row>
@@ -22739,7 +22739,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Yes.</t>
+          <t>Đúng vậy.</t>
         </is>
       </c>
     </row>
@@ -23454,7 +23454,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Không sao, tớ có thể kết nối thêm với mấy Quả Cầu Sonoro để hoạt động bình thường.</t>
+          <t>Không sao, tớ có thể kết nối thêm với mấy Sonoro Sphere để hoạt động bình thường.</t>
         </is>
       </c>
     </row>
@@ -23844,7 +23844,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Ý bạn là gì?</t>
+          <t>Ý anh là sao?</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Ta từng nghĩ nhiệm vụ của mình là bảo vệ Bờ Đen, tuân theo mọi mệnh lệnh của Hệ thống Tethys.</t>
+          <t>Tao từng nghĩ nhiệm vụ của mình là bảo vệ Bờ Đen, tuân theo mọi mệnh lệnh của Hệ thống Tethys.</t>
         </is>
       </c>
     </row>
@@ -24104,7 +24104,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Ngươi đã chia sẻ với ta biết bao điều—về thế giới bên ngoài, về chính ngươi, về quá khứ, hiện tại và tương lai.</t>
+          <t>Mày đã chia sẻ với tao biết bao điều—về thế giới bên ngoài, về chính mày, về quá khứ, hiện tại và tương lai.</t>
         </is>
       </c>
     </row>
@@ -26639,7 +26639,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Ý bạn là gì?</t>
+          <t>Ý anh là sao?</t>
         </is>
       </c>
     </row>
@@ -27419,7 +27419,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Ơ, Shorekeeper đâu rồi? Không phải cô ấy đi với cậu à?</t>
+          <t>Ơ, Shorekeeper đâu rồi? Không phải cô ấy đi với mày à?</t>
         </is>
       </c>
     </row>
@@ -28329,7 +28329,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Đang xác nhận quyền truy cập... {PlayerName}, Quản gia Trưởng. Chào mừng cậu.</t>
+          <t>Đang xác nhận quyền truy cập... {PlayerName}, Quản gia Trưởng. Chào mừng bạn.</t>
         </is>
       </c>
     </row>
@@ -28654,7 +28654,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Cậu... Cậu chính là—</t>
+          <t>Mày... Mày chính là—</t>
         </is>
       </c>
     </row>
@@ -29629,7 +29629,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Cậu đã nghe {Male=hắn;Female=cô ta} nói rồi đấy.</t>
+          <t>Cậu đã nghe {Male=he;Female=she} nói rồi đấy.</t>
         </is>
       </c>
     </row>
